--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396045</v>
+        <v>113396046</v>
       </c>
       <c r="B2" t="n">
         <v>56765</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578141</v>
+        <v>578112</v>
       </c>
       <c r="R2" t="n">
-        <v>6966558</v>
+        <v>6966557</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396047</v>
+        <v>113396045</v>
       </c>
       <c r="B3" t="n">
         <v>56765</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578061</v>
+        <v>578141</v>
       </c>
       <c r="R3" t="n">
-        <v>6966572</v>
+        <v>6966558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396046</v>
+        <v>113396048</v>
       </c>
       <c r="B4" t="n">
         <v>56765</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578112</v>
+        <v>578061</v>
       </c>
       <c r="R4" t="n">
-        <v>6966557</v>
+        <v>6966566</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396048</v>
+        <v>113396047</v>
       </c>
       <c r="B5" t="n">
         <v>56765</v>
@@ -1039,7 +1039,7 @@
         <v>578061</v>
       </c>
       <c r="R5" t="n">
-        <v>6966566</v>
+        <v>6966572</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396046</v>
+        <v>113396047</v>
       </c>
       <c r="B2" t="n">
         <v>56765</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578112</v>
+        <v>578061</v>
       </c>
       <c r="R2" t="n">
-        <v>6966557</v>
+        <v>6966572</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396047</v>
+        <v>113396046</v>
       </c>
       <c r="B5" t="n">
         <v>56765</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578061</v>
+        <v>578112</v>
       </c>
       <c r="R5" t="n">
-        <v>6966572</v>
+        <v>6966557</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396047</v>
+        <v>113396046</v>
       </c>
       <c r="B2" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578061</v>
+        <v>578112</v>
       </c>
       <c r="R2" t="n">
-        <v>6966572</v>
+        <v>6966557</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396045</v>
+        <v>113396048</v>
       </c>
       <c r="B3" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578141</v>
+        <v>578061</v>
       </c>
       <c r="R3" t="n">
-        <v>6966558</v>
+        <v>6966566</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396048</v>
+        <v>113396047</v>
       </c>
       <c r="B4" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>578061</v>
       </c>
       <c r="R4" t="n">
-        <v>6966566</v>
+        <v>6966572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396046</v>
+        <v>113396045</v>
       </c>
       <c r="B5" t="n">
-        <v>56765</v>
+        <v>56766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578112</v>
+        <v>578141</v>
       </c>
       <c r="R5" t="n">
-        <v>6966557</v>
+        <v>6966558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396046</v>
+        <v>113396047</v>
       </c>
       <c r="B2" t="n">
         <v>56766</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578112</v>
+        <v>578061</v>
       </c>
       <c r="R2" t="n">
-        <v>6966557</v>
+        <v>6966572</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396048</v>
+        <v>113396045</v>
       </c>
       <c r="B3" t="n">
         <v>56766</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578061</v>
+        <v>578141</v>
       </c>
       <c r="R3" t="n">
-        <v>6966566</v>
+        <v>6966558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396047</v>
+        <v>113396048</v>
       </c>
       <c r="B4" t="n">
         <v>56766</v>
@@ -932,7 +932,7 @@
         <v>578061</v>
       </c>
       <c r="R4" t="n">
-        <v>6966572</v>
+        <v>6966566</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396045</v>
+        <v>113396046</v>
       </c>
       <c r="B5" t="n">
         <v>56766</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578141</v>
+        <v>578112</v>
       </c>
       <c r="R5" t="n">
-        <v>6966558</v>
+        <v>6966557</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396047</v>
+        <v>113396045</v>
       </c>
       <c r="B2" t="n">
         <v>56766</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578061</v>
+        <v>578141</v>
       </c>
       <c r="R2" t="n">
-        <v>6966572</v>
+        <v>6966558</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396045</v>
+        <v>113396047</v>
       </c>
       <c r="B3" t="n">
         <v>56766</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578141</v>
+        <v>578061</v>
       </c>
       <c r="R3" t="n">
-        <v>6966558</v>
+        <v>6966572</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113396045</v>
       </c>
       <c r="B2" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396047</v>
+        <v>113396046</v>
       </c>
       <c r="B3" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578061</v>
+        <v>578112</v>
       </c>
       <c r="R3" t="n">
-        <v>6966572</v>
+        <v>6966557</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>113396048</v>
       </c>
       <c r="B4" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396046</v>
+        <v>113396047</v>
       </c>
       <c r="B5" t="n">
-        <v>56766</v>
+        <v>56769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578112</v>
+        <v>578061</v>
       </c>
       <c r="R5" t="n">
-        <v>6966557</v>
+        <v>6966572</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396045</v>
+        <v>113396047</v>
       </c>
       <c r="B2" t="n">
         <v>56769</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578141</v>
+        <v>578061</v>
       </c>
       <c r="R2" t="n">
-        <v>6966558</v>
+        <v>6966572</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396046</v>
+        <v>113396048</v>
       </c>
       <c r="B3" t="n">
         <v>56769</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578112</v>
+        <v>578061</v>
       </c>
       <c r="R3" t="n">
-        <v>6966557</v>
+        <v>6966566</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396048</v>
+        <v>113396046</v>
       </c>
       <c r="B4" t="n">
         <v>56769</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578061</v>
+        <v>578112</v>
       </c>
       <c r="R4" t="n">
-        <v>6966566</v>
+        <v>6966557</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396047</v>
+        <v>113396045</v>
       </c>
       <c r="B5" t="n">
         <v>56769</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578061</v>
+        <v>578141</v>
       </c>
       <c r="R5" t="n">
-        <v>6966572</v>
+        <v>6966558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396047</v>
+        <v>113396046</v>
       </c>
       <c r="B2" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578061</v>
+        <v>578112</v>
       </c>
       <c r="R2" t="n">
-        <v>6966572</v>
+        <v>6966557</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
         <v>113396048</v>
       </c>
       <c r="B3" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396046</v>
+        <v>113396047</v>
       </c>
       <c r="B4" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578112</v>
+        <v>578061</v>
       </c>
       <c r="R4" t="n">
-        <v>6966557</v>
+        <v>6966572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +999,7 @@
         <v>113396045</v>
       </c>
       <c r="B5" t="n">
-        <v>56769</v>
+        <v>56773</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396048</v>
+        <v>113396045</v>
       </c>
       <c r="B3" t="n">
         <v>56773</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578061</v>
+        <v>578141</v>
       </c>
       <c r="R3" t="n">
-        <v>6966566</v>
+        <v>6966558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396047</v>
+        <v>113396048</v>
       </c>
       <c r="B4" t="n">
         <v>56773</v>
@@ -932,7 +932,7 @@
         <v>578061</v>
       </c>
       <c r="R4" t="n">
-        <v>6966572</v>
+        <v>6966566</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396045</v>
+        <v>113396047</v>
       </c>
       <c r="B5" t="n">
         <v>56773</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578141</v>
+        <v>578061</v>
       </c>
       <c r="R5" t="n">
-        <v>6966558</v>
+        <v>6966572</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113396046</v>
       </c>
       <c r="B2" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396045</v>
+        <v>113396047</v>
       </c>
       <c r="B3" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578141</v>
+        <v>578061</v>
       </c>
       <c r="R3" t="n">
-        <v>6966558</v>
+        <v>6966572</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>113396048</v>
       </c>
       <c r="B4" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396047</v>
+        <v>113396045</v>
       </c>
       <c r="B5" t="n">
-        <v>56773</v>
+        <v>56780</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578061</v>
+        <v>578141</v>
       </c>
       <c r="R5" t="n">
-        <v>6966572</v>
+        <v>6966558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113396046</v>
       </c>
       <c r="B2" t="n">
-        <v>56780</v>
+        <v>56782</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396047</v>
+        <v>113396045</v>
       </c>
       <c r="B3" t="n">
-        <v>56780</v>
+        <v>56782</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578061</v>
+        <v>578141</v>
       </c>
       <c r="R3" t="n">
-        <v>6966572</v>
+        <v>6966558</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +892,7 @@
         <v>113396048</v>
       </c>
       <c r="B4" t="n">
-        <v>56780</v>
+        <v>56782</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396045</v>
+        <v>113396047</v>
       </c>
       <c r="B5" t="n">
-        <v>56780</v>
+        <v>56782</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578141</v>
+        <v>578061</v>
       </c>
       <c r="R5" t="n">
-        <v>6966558</v>
+        <v>6966572</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396046</v>
+        <v>113396045</v>
       </c>
       <c r="B2" t="n">
-        <v>56782</v>
+        <v>56810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578112</v>
+        <v>578141</v>
       </c>
       <c r="R2" t="n">
-        <v>6966557</v>
+        <v>6966558</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396045</v>
+        <v>113396047</v>
       </c>
       <c r="B3" t="n">
-        <v>56782</v>
+        <v>56810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578141</v>
+        <v>578061</v>
       </c>
       <c r="R3" t="n">
-        <v>6966558</v>
+        <v>6966572</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396048</v>
+        <v>113396046</v>
       </c>
       <c r="B4" t="n">
-        <v>56782</v>
+        <v>56810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578061</v>
+        <v>578112</v>
       </c>
       <c r="R4" t="n">
-        <v>6966566</v>
+        <v>6966557</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396047</v>
+        <v>113396048</v>
       </c>
       <c r="B5" t="n">
-        <v>56782</v>
+        <v>56810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>578061</v>
       </c>
       <c r="R5" t="n">
-        <v>6966572</v>
+        <v>6966566</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113396045</v>
+        <v>113396046</v>
       </c>
       <c r="B2" t="n">
         <v>56810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578141</v>
+        <v>578112</v>
       </c>
       <c r="R2" t="n">
-        <v>6966558</v>
+        <v>6966557</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396046</v>
+        <v>113396048</v>
       </c>
       <c r="B4" t="n">
         <v>56810</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578112</v>
+        <v>578061</v>
       </c>
       <c r="R4" t="n">
-        <v>6966557</v>
+        <v>6966566</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396048</v>
+        <v>113396045</v>
       </c>
       <c r="B5" t="n">
         <v>56810</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578061</v>
+        <v>578141</v>
       </c>
       <c r="R5" t="n">
-        <v>6966566</v>
+        <v>6966558</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113396045</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>113396048</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>113396046</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>113396047</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113396045</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>113396048</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>113396046</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>113396047</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113396045</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>113396048</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>113396046</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>113396047</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113396045</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>113396048</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>113396046</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>113396047</v>
       </c>
       <c r="B5" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113396045</v>
       </c>
       <c r="B2" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113396048</v>
+        <v>113396046</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578061</v>
+        <v>578112</v>
       </c>
       <c r="R3" t="n">
-        <v>6966566</v>
+        <v>6966557</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113396046</v>
+        <v>113396047</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578112</v>
+        <v>578061</v>
       </c>
       <c r="R4" t="n">
-        <v>6966557</v>
+        <v>6966572</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113396047</v>
+        <v>113396048</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,7 +1019,7 @@
         <v>578061</v>
       </c>
       <c r="R5" t="n">
-        <v>6966572</v>
+        <v>6966566</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 49863-2023 artfynd.xlsx
+++ b/artfynd/A 49863-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113396045</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113396046</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113396047</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,8 +1100,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113396048</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>